--- a/base/pacotes/placon-arminio-tavares/executivo-placon-arminio-tavares.xlsx
+++ b/base/pacotes/placon-arminio-tavares/executivo-placon-arminio-tavares.xlsx
@@ -231,6 +231,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -241,9 +244,6 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 2026-04-13T17:11:38 | AC=4077 m² | UR=55 | baseado em 5 projetos similares</t>
+          <t>Gerado em 2026-04-13T22:57:54 | AC=4077 m² | UR=55 | baseado em 5 projetos similares</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
         <v>0.07528467305884261</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>0.06549338640256483</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>0.05851872528957302</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>0.01313648811895521</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0.1031317396726247</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>0.01703288564805291</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1487,29 +1487,29 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Ar condicionado Cassete Circular 36.000 BTU</t>
+          <t>Instalação de Exaustor tipo Vento Kit *</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>15099</v>
+        <v>222.14</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>15099</v>
+        <v>12217.7</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>xpcon-marena</t>
+          <t>paludo-volo-home</t>
         </is>
       </c>
     </row>
@@ -1519,29 +1519,29 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Instalação de Exaustor tipo Vento Kit *</t>
+          <t>Ar condicionado Split 18.000 BTU/H - 18.000 BTU/h</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>222.14</v>
+        <v>4299</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>12217.7</v>
+        <v>4299</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Ar condicionado Split 30.000 BTU/H - 30.000 BTU/h</t>
+          <t>Ar condicionado Split 12.000 BTU/H - 12.000 BTU/h</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -1563,10 +1563,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>8018.1</v>
+        <v>3139</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>8018.1</v>
+        <v>3139</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Ar condicionado Split 18.000 BTU/H - 18.000 BTU/h</t>
+          <t>Terminal de ventilação ciruclar plastico 100mm - 100</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -1592,13 +1592,13 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>4299</v>
+        <v>995</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>4299</v>
+        <v>1990</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Ar condicionado Split 12.000 BTU/H - 12.000 BTU/h</t>
+          <t>Renovador de ar 100mm - 100mm</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>3139</v>
+        <v>404.99</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>3139</v>
+        <v>809.98</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Terminal de ventilação ciruclar plastico 100mm - 100</t>
+          <t>Tubo de Cobre Flexível para Ar Condicionado (L) - 1/4"</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>2</v>
+        <v>48.495</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>995</v>
+        <v>14.4</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>1990</v>
+        <v>698.3280000000001</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
@@ -1679,22 +1679,22 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Renovador de ar 100mm - 100mm</t>
+          <t>Tubo de Cobre Flexível para Ar Condicionado (S) - 1/2"</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>2</v>
+        <v>29.94</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>404.99</v>
+        <v>24.985</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>809.98</v>
+        <v>748.0509000000001</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Tubo de Cobre Flexível para Ar Condicionado (L) - 1/4"</t>
+          <t>Eletroduto Flexível Tipo Leve - 3/4"</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -1720,13 +1720,13 @@
         </is>
       </c>
       <c r="D12" s="25" t="n">
-        <v>48.495</v>
+        <v>68.825</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>14.4</v>
+        <v>3.38</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>698.3280000000001</v>
+        <v>232.6285</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Tubo de Cobre Flexível para Ar Condicionado (S) - 1/2"</t>
+          <t>Tubo - PVC Esgoto - Série Normal - 100</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>29.94</v>
+        <v>13.27</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>24.985</v>
+        <v>12.88</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>748.0509000000001</v>
+        <v>170.9176</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
@@ -1775,22 +1775,22 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Eletroduto Flexível Tipo Leve - 3/4"</t>
+          <t>Ar Condicionado</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Ar Condicionado</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>68.825</v>
+        <v>32094.9419</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>3.38</v>
+        <v>105.0499</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>232.6285</v>
+        <v>3371570.43710081</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Tubo - PVC Esgoto - Série Normal - 100</t>
+          <t>Isolamento Térmico (S) - 12 mm</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -1816,13 +1816,13 @@
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>13.27</v>
+        <v>48.54</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>12.88</v>
+        <v>1.8</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>170.9176</v>
+        <v>87.372</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -1839,22 +1839,22 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Ar Condicionado</t>
+          <t>Isolamento Térmico (L) - 6 mm</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>Ar Condicionado</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>32094.9419</v>
+        <v>48.54</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>105.0499</v>
+        <v>1.45</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>3371570.43710081</v>
+        <v>70.383</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Isolamento Térmico (S) - 12 mm</t>
+          <t>Isolamento Térmico (S) - 18 mm</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>48.54</v>
+        <v>27.095</v>
       </c>
       <c r="E17" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>87.372</v>
+        <v>48.771</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
@@ -1903,22 +1903,22 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Isolamento Térmico (L) - 6 mm</t>
+          <t>Joelho 90º - ø100xø100</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>48.54</v>
+        <v>3</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>1.45</v>
+        <v>7.81</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>70.383</v>
+        <v>23.43</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Isolamento Térmico (S) - 18 mm</t>
+          <t>Isolamento Térmico (L) - 10 mm</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -1947,10 +1947,10 @@
         <v>27.095</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>48.771</v>
+        <v>41.99725</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Joelho 90º - ø100xø100</t>
+          <t>Caixa de passagem: 24.000 BTU/H - 24.000 BTU/h</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>7.81</v>
+        <v>18.66</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>23.43</v>
+        <v>37.32</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
@@ -1999,22 +1999,22 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Isolamento Térmico (L) - 10 mm</t>
+          <t>Caixa de passagem: 12.000 BTU/H - 12.000 BTU/h</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>27.095</v>
+        <v>4</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>1.55</v>
+        <v>7.92</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>41.99725</v>
+        <v>31.68</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Caixa de passagem: 24.000 BTU/H - 24.000 BTU/h</t>
+          <t>Luva Simples 100mm, Esgoto Série Normal - TIGRE - ø100xø100</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="D22" s="25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>18.66</v>
+        <v>5.04</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>37.32</v>
+        <v>15.12</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Caixa de passagem: 12.000 BTU/H - 12.000 BTU/h</t>
+          <t>Luva Soldável com Rosca 25 x 1/2'' - ø25xø20</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -2072,13 +2072,13 @@
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>7.92</v>
+        <v>3.97</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>31.68</v>
+        <v>27.79</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Luva Simples 100mm, Esgoto Série Normal - TIGRE - ø100xø100</t>
+          <t>Caixa de passagem: 30.000 BTU/H - 30.000 BTU/h</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>5.04</v>
+        <v>22.9</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>15.12</v>
+        <v>22.9</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Luva Soldável com Rosca 25 x 1/2'' - ø25xø20</t>
+          <t>Caixa de passagem: 18.000 BTU/H - 18.000 BTU/h</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -2136,82 +2136,18 @@
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>3.97</v>
+        <v>12.8</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>27.79</v>
+        <v>12.8</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="24" t="inlineStr">
-        <is>
-          <t>xpcon-marena</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="24" t="inlineStr">
-        <is>
-          <t>Caixa de passagem: 30.000 BTU/H - 30.000 BTU/h</t>
-        </is>
-      </c>
-      <c r="C26" s="23" t="inlineStr">
-        <is>
-          <t>pç</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="26" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="F26" s="27" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G26" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="24" t="inlineStr">
-        <is>
-          <t>xpcon-marena</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="24" t="inlineStr">
-        <is>
-          <t>Caixa de passagem: 18.000 BTU/H - 18.000 BTU/h</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>pç</t>
-        </is>
-      </c>
-      <c r="D27" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="26" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F27" s="27" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>xpcon-marena</t>
         </is>
@@ -3309,7 +3245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3384,22 +3320,22 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Esquadrias de Alumínio</t>
+          <t>Kit porta de abrir de madeira, folha leve/média, 70x210cm, fixação com espuma expansiva - sem ferragens - incluso instalação*</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>982359.8100000001</v>
+        <v>728.8454</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>982359.8100000001</v>
+        <v>56121.0958</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
@@ -3416,22 +3352,22 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Revestimento de Fachada com Brise metálico *</t>
+          <t>Kit porta de abrir de madeira, folha leve/média, 80x210cm, fixação com espuma expansiva - sem ferragens - incluso instalação*</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>un</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>96675</v>
+        <v>728.8454</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>96675</v>
+        <v>40086.497</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
@@ -3448,7 +3384,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Kit porta de abrir de madeira, folha leve/média, 70x210cm, fixação com espuma expansiva - sem ferragens - incluso instalação*</t>
+          <t>Kit porta de abrir de madeira, folha leve/média, 90x210cm, fixação com espuma expansiva - sem ferragens - incluso instalação*</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -3457,13 +3393,13 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>728.8454</v>
+        <v>802.8454</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>56121.0958</v>
+        <v>24085.362</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -3480,22 +3416,22 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Portões de alumínio *</t>
+          <t>Contramarco de alumínio, fixação com argamassa, incluso mão de obra</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>995.28</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>41259.26</v>
+        <v>15.2264</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>41259.26</v>
+        <v>15154.531392</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
@@ -3512,7 +3448,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Kit porta de abrir de madeira, folha leve/média, 80x210cm, fixação com espuma expansiva - sem ferragens - incluso instalação*</t>
+          <t>Porta Corta Fogo 0.90x2.10m Completa</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -3521,146 +3457,18 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>728.8454</v>
+        <v>1250</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>40086.497</v>
+        <v>8750</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Kit porta de abrir de madeira, folha leve/média, 90x210cm, fixação com espuma expansiva - sem ferragens - incluso instalação*</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>30</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>802.8454</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>24085.362</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Pele de vidro *</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>17273.35</v>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>17273.35</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Contramarco de alumínio, fixação com argamassa, incluso mão de obra</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="n">
-        <v>995.28</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>15.2264</v>
-      </c>
-      <c r="F12" s="27" t="n">
-        <v>15154.531392</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>Porta Corta Fogo 0.90x2.10m Completa</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>un</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>8750</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>paludo-volo-home</t>
         </is>
@@ -4375,29 +4183,25 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Paisagismo - Material e mão de obra*</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Espreguiçadeira Brisa Estofado Navy Base Alumínio Taupe - 75469 - Sun House</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr"/>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>53582</v>
+        <v>5205.2</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>53582</v>
+        <v>20820.8</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -4407,29 +4211,25 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Limpeza final *</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Cortina</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr"/>
       <c r="D7" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>27791.56</v>
+        <v>2900</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>27791.56</v>
+        <v>14500</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>arv-ingleses-spot, xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4439,25 +4239,25 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Esteira Profissional Adidas T-23 (T-23) - Adidas</t>
+          <t>Acabamentos Especiais</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr"/>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>38.03</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>25172</v>
+        <v>450</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>25172</v>
+        <v>17113.5</v>
       </c>
       <c r="G8" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>xpcon-marena</t>
+          <t>arv-ingleses-spot, xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4467,25 +4267,25 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Marcenaria</t>
+          <t>ESTANTE PARA DUMBELL 10 PARES (TAC 043) - TITANIUM ESSENTIAL</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr"/>
       <c r="D9" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>21000</v>
+        <v>5099.99</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>21000</v>
+        <v>10199.98</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot, xpcon-marena</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4495,18 +4295,18 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Espreguiçadeira Brisa Estofado Navy Base Alumínio Taupe - 75469 - Sun House</t>
+          <t>Poltrona Externa Lunna - Wood</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr"/>
       <c r="D10" s="25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>5205.2</v>
+        <v>4774.44</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>20820.8</v>
+        <v>9548.879999999999</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
@@ -4523,25 +4323,25 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Estação Funcional Trainer Athletic 2400MS Com 67,5kg +40 exercícios</t>
+          <t>Cadeira Leme com Detalhe em Recouro e Braços, em Madeira Maciça</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr"/>
       <c r="D11" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>18590</v>
+        <v>1158.46</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>18590</v>
+        <v>9267.68</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>xpcon-marena</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -4551,25 +4351,25 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Kit de 10 Pares de Dumbell 12 a 30 Kg (Kit Dum 10P) - FIT4</t>
+          <t>Conjunto com Mesa Ripada + 4 Cadeiras de Jardim e Piscina + Ombrelone com Base Preto</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr"/>
       <c r="D12" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>16111.2</v>
+        <v>4598</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>16111.2</v>
+        <v>9196</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="24" t="inlineStr">
         <is>
-          <t>xpcon-marena</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -4579,25 +4379,25 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Cortina</t>
+          <t>Cadeira Área Externa de Alumínio Carmy com Corda Naútica Grafite/Amêndoa G56 - Gran Belo</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr"/>
       <c r="D13" s="25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>2900</v>
+        <v>890.91</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>14500</v>
+        <v>8909.1</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot, xpcon-marena</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -4607,25 +4407,25 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Acabamentos Especiais</t>
+          <t>Mesa Dobravel Quadrada Primavera Stain Castanho 90cm - 34793 Sun House</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr"/>
       <c r="D14" s="25" t="n">
-        <v>38.03</v>
+        <v>5</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>450</v>
+        <v>1484.56</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>17113.5</v>
+        <v>7422.799999999999</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot, xpcon-marena</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -4635,25 +4435,29 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>Spinning Profissional Adidas (C-21X) - Adidas</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr"/>
+          <t>Calçada em paver</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
       <c r="D15" s="25" t="n">
-        <v>1</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>14350</v>
+        <v>82</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>14350</v>
+        <v>7367.7</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="24" t="inlineStr">
         <is>
-          <t>xpcon-marena</t>
+          <t>paludo-volo-home</t>
         </is>
       </c>
     </row>
@@ -4663,25 +4467,25 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Mesa de Jantar Retangular com Tampo de Madeira e Aço Inox V Shape 2,50m X 1,00m</t>
+          <t>Cadeira de Aço Carbono Estofada Moderna Logos Bouclê Off White / Cinza</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr"/>
       <c r="D16" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>13300</v>
+        <v>1115</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>13300</v>
+        <v>6690</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4691,25 +4495,25 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Ice Maker de Embuitir Evol Smart JG36I Inox 220V</t>
+          <t>Kit 10 pares de halteres emb. De 1 a 10 KG (Kit H 10) - FIT4</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr"/>
       <c r="D17" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>13299.05</v>
+        <v>3264.8</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>13299.05</v>
+        <v>6529.6</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4719,25 +4523,25 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>Chopeira Naja Italiana  Premium</t>
+          <t>Poltronas Decorativas Para Sala De Estar Base Fixa Londres L02 Bouclê Terracota - Lyam</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr"/>
       <c r="D18" s="25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>12784</v>
+        <v>745</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>12784</v>
+        <v>5960</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="24" t="inlineStr">
         <is>
-          <t>xpcon-marena</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -4747,25 +4551,25 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>Playground em madeira</t>
+          <t>Poltrona Delgada - Lider Interiores</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr"/>
       <c r="D19" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>10899</v>
+        <v>2890</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>10899</v>
+        <v>5780</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="24" t="inlineStr">
         <is>
-          <t>xpcon-marena</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -4775,18 +4579,18 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>ESTANTE PARA DUMBELL 10 PARES (TAC 043) - TITANIUM ESSENTIAL</t>
+          <t>Piso de borracha para playground</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr"/>
       <c r="D20" s="25" t="n">
-        <v>2</v>
+        <v>17.06</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>5099.99</v>
+        <v>299.9</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>10199.98</v>
+        <v>5116.293999999999</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
@@ -4803,7 +4607,7 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Mesa triangular Concreto &amp; Granilite | uso área externo</t>
+          <t>Mesa Bouman Solo Concreto &amp; Granilite | uso área externo</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr"/>
@@ -4811,10 +4615,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>9765</v>
+        <v>5000</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>9765</v>
+        <v>5000</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
@@ -4831,25 +4635,25 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>Poltrona Externa Lunna - Wood</t>
+          <t>Forno Elétrico de Embutir Brastemp 67L Inox com Função Ar Forçado e Painel Touch BO260AR</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr"/>
       <c r="D22" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>4774.44</v>
+        <v>4892.49</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>9548.879999999999</v>
+        <v>4892.49</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4859,18 +4663,18 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Leme com Detalhe em Recouro e Braços, em Madeira Maciça</t>
+          <t>Banqueta Alta de Madeira Palla Estofada com Braços - (IMC) Branco</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr"/>
       <c r="D23" s="25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>1158.46</v>
+        <v>1626.88</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>9267.68</v>
+        <v>4880.64</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
@@ -4887,25 +4691,25 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>Conjunto com Mesa Ripada + 4 Cadeiras de Jardim e Piscina + Ombrelone com Base Preto</t>
+          <t>Mesa de Jantar Orgânica Cloe de Madeira com Tampo de Vidro</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr"/>
       <c r="D24" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>4598</v>
+        <v>4738</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>9196</v>
+        <v>4738</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4915,18 +4719,18 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>Sofá Em Couro Caramelo - DEENI</t>
+          <t>Mesa redonda mendoza 90 cm</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr"/>
       <c r="D25" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>9150.34</v>
+        <v>2249</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>9150.34</v>
+        <v>4498</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
@@ -4943,25 +4747,25 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>Cadeira Área Externa de Alumínio Carmy com Corda Naútica Grafite/Amêndoa G56 - Gran Belo</t>
+          <t>Mesa Cônica Oval 1.80 X 1.00 Tampo Mármore Branco Esp. Santo</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr"/>
       <c r="D26" s="25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>890.91</v>
+        <v>4200</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>8909.1</v>
+        <v>4200</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4775,7 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>Sofá boreal - moderno - living - estofados jardim</t>
+          <t>Sofá Curvo</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr"/>
@@ -4979,17 +4783,17 @@
         <v>1</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>8500</v>
+        <v>4194</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>8500</v>
+        <v>4194</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -4999,18 +4803,18 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>Bancadas mármore</t>
+          <t>Cadeira com Braço Flemish</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr"/>
       <c r="D28" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>8000</v>
+        <v>836.8099999999999</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>8000</v>
+        <v>4184.049999999999</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>1</v>
@@ -5027,29 +4831,25 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>Mobiliário de apoio a obra *</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
+          <t>Sofá Suspenso Slim</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr"/>
       <c r="D29" s="25" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>7978.02</v>
+        <v>4150</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>7978.02</v>
+        <v>4150</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H29" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -5059,7 +4859,7 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>Geladeira Brastemp French Door Frost Free A+++ 554l Inox Bro85ak</t>
+          <t>Marcenaria</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr"/>
@@ -5067,10 +4867,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>7750</v>
+        <v>4000</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>7750</v>
+        <v>4000</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
@@ -5087,25 +4887,25 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Sofá Kaeda Corda Náutica Madeira Eucalipto Design Artesanal</t>
+          <t>Cadeira da mesa de jantar</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr"/>
       <c r="D31" s="25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>7700.45</v>
+        <v>379</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>7700.45</v>
+        <v>3790</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -5115,25 +4915,25 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Mesa Dobravel Quadrada Primavera Stain Castanho 90cm - 34793 Sun House</t>
+          <t>Refrigerador Expositor Vertical Eos Eco Gelo 124l Eev120p Preto</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr"/>
       <c r="D32" s="25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1484.56</v>
+        <v>1789</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>7422.799999999999</v>
+        <v>3578</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="24" t="inlineStr">
         <is>
-          <t>arv-ingleses-spot</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -5143,29 +4943,25 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Calçada em paver</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
+          <t>Tapete Cuenca Bege 2,40x3,50</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr"/>
       <c r="D33" s="25" t="n">
-        <v>89.84999999999999</v>
+        <v>1</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>82</v>
+        <v>3293</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>7367.7</v>
+        <v>3293</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -5175,25 +4971,25 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>Sofá Ilha com Encosto e Almofadas Delta 435cm Modulado Chaise e Puffs Veludo Cinza G52 - Gran Belo</t>
+          <t>Quadro Decorativo 1 Tela: Obra Abstrata Moderna e Sofisticada</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr"/>
       <c r="D34" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>6881</v>
+        <v>1200</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>6881</v>
+        <v>2400</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="24" t="inlineStr">
         <is>
-          <t>xpcon-marena</t>
+          <t>arv-ingleses-spot</t>
         </is>
       </c>
     </row>
@@ -5283,36 +5079,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>Despesas com Imprevistos *</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D5" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>185693.21</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>185693.21</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5330,7 +5102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5405,59 +5177,27 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Alvará Habite-se *</t>
+          <t>Alvarás, Licenças e Taxas de Aprovação *</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>3972.3</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>17491.56</v>
+        <v>3.1727</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>17491.56</v>
+        <v>12602.91621</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>Alvarás, Licenças e Taxas de Aprovação *</t>
-        </is>
-      </c>
-      <c r="C6" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>3972.3</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>3.1727</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>12602.91621</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>paludo-volo-home</t>
         </is>
@@ -5530,7 +5270,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="n">
+      <c r="A4" s="29" t="n">
         <v>1</v>
       </c>
       <c r="B4" s="18" t="inlineStr">
@@ -5538,19 +5278,19 @@
           <t>xpcon-marena</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="30" t="n">
         <v>4174.83</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="31" t="n"/>
+      <c r="F4" s="32" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="29" t="n">
         <v>2</v>
       </c>
       <c r="B5" s="18" t="inlineStr">
@@ -5558,19 +5298,19 @@
           <t>paludo-volo-home</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="30" t="n">
         <v>3972.3</v>
       </c>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="30" t="n">
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="31" t="n">
         <v>3134.37</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="32" t="n">
         <v>12450664.73</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="29" t="n">
         <v>3</v>
       </c>
       <c r="B6" s="18" t="inlineStr">
@@ -5578,19 +5318,19 @@
           <t>arv-ingleses-spot</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>2618.24</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="29" t="n">
         <v>49</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="31" t="n"/>
+      <c r="F6" s="32" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n">
+      <c r="A7" s="29" t="n">
         <v>4</v>
       </c>
       <c r="B7" s="18" t="inlineStr">
@@ -5598,19 +5338,19 @@
           <t>libra-concept-libra-conecpt</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="30" t="n">
         <v>4338.77</v>
       </c>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="30" t="n">
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="31" t="n">
         <v>2271.01</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="32" t="n">
         <v>9853382.76</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="n">
+      <c r="A8" s="29" t="n">
         <v>5</v>
       </c>
       <c r="B8" s="18" t="inlineStr">
@@ -5618,14 +5358,14 @@
           <t>macom-adda</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>4358.27</v>
       </c>
-      <c r="D8" s="28" t="n"/>
-      <c r="E8" s="30" t="n">
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="31" t="n">
         <v>3082.6</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="32" t="n">
         <v>13434812.16</v>
       </c>
     </row>
@@ -6017,17 +5757,17 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>Unidade construtiva 1</t>
         </is>
       </c>
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>TERRENO, DESPESAS ADM E CUSTOS INDIRETOS</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
@@ -6197,7 +5937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6272,22 +6012,22 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Infraestrutura para instalação de ar condicionado *</t>
+          <t>Movimentação de terra para bota-fora - sapatas e vigas*</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>5520.25</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>122494.95</v>
+        <v>15.0012</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>122494.95</v>
+        <v>82810.37430000001</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
@@ -6304,22 +6044,22 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Movimentação de terra para bota-fora - sapatas e vigas*</t>
+          <t>Fabricação, montagem e desmontagem de fôrma para viga baldrame, em chapa de madeira compensada resinada e=14mm, 2 utilizações *</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>5520.25</v>
+        <v>591.3099999999999</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>15.0012</v>
+        <v>57.3846</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>82810.37430000001</v>
+        <v>33932.087826</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
@@ -6336,22 +6076,22 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Fabricação, montagem e desmontagem de fôrma para viga baldrame, em chapa de madeira compensada resinada e=14mm, 2 utilizações *</t>
+          <t>Escavação mecanizada para blocos de fundação e vigas baldrame, com previsão de forma, com retroescavadeira *</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>591.3099999999999</v>
+        <v>411</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>57.3846</v>
+        <v>78.9781</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>33932.087826</v>
+        <v>32459.9991</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -6368,91 +6108,27 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Escavação mecanizada para blocos de fundação e vigas baldrame, com previsão de forma, com retroescavadeira *</t>
+          <t>Fabricação, montagem e desmontagem de fôrma para sapata, em chapa de madeira compensada resinada e=14mm</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>411</v>
+        <v>456.32</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>78.9781</v>
+        <v>54.3148</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>32459.9991</v>
+        <v>24784.929536</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>Fabricação, montagem e desmontagem de fôrma para sapata, em chapa de madeira compensada resinada e=14mm</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>456.32</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>54.3148</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>24784.929536</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Projeto de Fundação *</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>8000</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>paludo-volo-home</t>
         </is>
@@ -8180,29 +7856,29 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Fios e cabos elétricos - Térreo *</t>
+          <t>AUTOMAÇÃO - Persiana Motorizada</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>71587.19</v>
+        <v>3021.8</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>71587.19</v>
+        <v>12087.2</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8212,29 +7888,29 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Quadros elétricos e disjuntores - Térreo *</t>
+          <t>Válvula redutora de pressão: 42LP 1.1/4" - BERMAD - ø32xø32</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>38366.49</v>
+        <v>4738</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>38366.49</v>
+        <v>9476</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8244,29 +7920,29 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Automação e sistemas lógicos e telecomunicação*</t>
+          <t>PEAD - Polietileno de Alta Densidade - 1.1/2"</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>1</v>
+        <v>261.31</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>35010.81</v>
+        <v>29.15</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>35010.81</v>
+        <v>7617.1865</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8276,29 +7952,29 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Instalações Elétricas Provisórias *</t>
+          <t>Filtro T compact 2" - BERMAD - ø50xø50</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>21865.14</v>
+        <v>4779.28</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>21865.14</v>
+        <v>7168.92</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8308,7 +7984,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>AUTOMAÇÃO - Persiana Motorizada</t>
+          <t>Caixa Sifonada com Grelha e Porta Grelha Redondos com 3 Entradas - DN 100 x 150 x 50mm - ø100xø150xø50</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -8317,13 +7993,13 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>3021.8</v>
+        <v>100</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>12087.2</v>
+        <v>7000</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
@@ -8340,29 +8016,29 @@
       </c>
       <c r="B10" s="24" t="inlineStr">
         <is>
-          <t>Projeto elétrico *</t>
+          <t>PEAD - Polietileno de Alta Densidade - 2"</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D10" s="25" t="n">
-        <v>1</v>
+        <v>89.3</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>10000</v>
+        <v>44.44</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>10000</v>
+        <v>3968.492</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8372,29 +8048,29 @@
       </c>
       <c r="B11" s="24" t="inlineStr">
         <is>
-          <t>Projeto hidrossanitário *</t>
+          <t>CAIXA DE PASSAGEM - PISO - Tampa 90x70 - B125 - Padrão CELESC</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E11" s="26" t="n">
-        <v>10000</v>
+        <v>1640.4</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>10000</v>
+        <v>4101</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8080,7 @@
       </c>
       <c r="B12" s="24" t="inlineStr">
         <is>
-          <t>Válvula redutora de pressão: 42LP 1.1/4" - BERMAD - ø32xø32</t>
+          <t>Conforme apresentado no Esquema Vertical - ESQUEMA VERTICAL ( AQUA-UP-H02-70/7)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -8416,10 +8092,10 @@
         <v>2</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>4738</v>
+        <v>1500</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>9476</v>
+        <v>3000</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>1</v>
@@ -8436,29 +8112,29 @@
       </c>
       <c r="B13" s="24" t="inlineStr">
         <is>
-          <t>Instalações preventivas *</t>
+          <t>TOMADAS DE TELEFONE, TV E DADOS - Dock de Som</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>8777.299999999999</v>
+        <v>1500</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>8777.299999999999</v>
+        <v>3000</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8468,29 +8144,29 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>Projeto preventivo contra incêndio *</t>
+          <t>Registro de gaveta Industrial 2 1/2" - DocolBásicos - ø75xø75</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E14" s="26" t="n">
-        <v>8420.48</v>
+        <v>292.9</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>8420.48</v>
+        <v>2636.1</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8176,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>PEAD - Polietileno de Alta Densidade - 1.1/2"</t>
+          <t>XLPE - 1kV (Prysmian) - 120 mm² - Azul claro</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -8509,13 +8185,13 @@
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>261.31</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>29.15</v>
+        <v>24.84</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>7617.1865</v>
+        <v>1947.456</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>1</v>
@@ -8532,22 +8208,22 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>Filtro T compact 2" - BERMAD - ø50xø50</t>
+          <t>XLPE - 1kV (Prysmian) - 120 mm² - Branco</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D16" s="25" t="n">
-        <v>1.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>4779.28</v>
+        <v>24.84</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>7168.92</v>
+        <v>1947.456</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>1</v>
@@ -8564,22 +8240,22 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>Caixa Sifonada com Grelha e Porta Grelha Redondos com 3 Entradas - DN 100 x 150 x 50mm - ø100xø150xø50</t>
+          <t>XLPE - 1kV (Prysmian) - 120 mm² - Preto</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D17" s="25" t="n">
-        <v>70</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>100</v>
+        <v>24.84</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>7000</v>
+        <v>1947.456</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>1</v>
@@ -8596,7 +8272,7 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>PEAD - Polietileno de Alta Densidade - 2"</t>
+          <t>XLPE - 1kV (Prysmian) - 120 mm² - Vermelho</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -8605,13 +8281,13 @@
         </is>
       </c>
       <c r="D18" s="25" t="n">
-        <v>89.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E18" s="26" t="n">
-        <v>44.44</v>
+        <v>24.84</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>3968.492</v>
+        <v>1947.456</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>1</v>
@@ -8628,7 +8304,7 @@
       </c>
       <c r="B19" s="24" t="inlineStr">
         <is>
-          <t>CAIXA DE PASSAGEM - PISO - Tampa 90x70 - B125 - Padrão CELESC</t>
+          <t>QUADRO DE DISTRIBUIÇÃO CARREGADOR VEICULAR - 1800X800X250 até 30</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -8637,13 +8313,13 @@
         </is>
       </c>
       <c r="D19" s="25" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>1640.4</v>
+        <v>2500</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>4101</v>
+        <v>2500</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>1</v>
@@ -8660,29 +8336,29 @@
       </c>
       <c r="B20" s="24" t="inlineStr">
         <is>
-          <t>Elaboração do Programa de Prevenção dos Riscos Ambientais (PPRA)*</t>
+          <t>CAIXA DE PASSAGEM - PISO - Tampa 65x45 - R1</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D20" s="25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>3498.18</v>
+        <v>560.1799999999999</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>3498.18</v>
+        <v>2240.72</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8368,7 @@
       </c>
       <c r="B21" s="24" t="inlineStr">
         <is>
-          <t>Conforme apresentado no Esquema Vertical - ESQUEMA VERTICAL ( AQUA-UP-H02-70/7)</t>
+          <t>Válvula redutora de pressão 42LP - 3/4" - ø20xø20</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -8701,13 +8377,13 @@
         </is>
       </c>
       <c r="D21" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="26" t="n">
-        <v>1500</v>
+        <v>1984.85</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>3000</v>
+        <v>1984.85</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>1</v>
@@ -8724,7 +8400,7 @@
       </c>
       <c r="B22" s="24" t="inlineStr">
         <is>
-          <t>TOMADAS DE TELEFONE, TV E DADOS - Dock de Som</t>
+          <t>Filtro de água pluvial: ACQUASAVE VF1 - ø150xø100xø150xø100</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -8733,13 +8409,13 @@
         </is>
       </c>
       <c r="D22" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>1500</v>
+        <v>1980</v>
       </c>
       <c r="F22" s="27" t="n">
-        <v>3000</v>
+        <v>1980</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>1</v>
@@ -8756,22 +8432,22 @@
       </c>
       <c r="B23" s="24" t="inlineStr">
         <is>
-          <t>Registro de gaveta Industrial 2 1/2" - DocolBásicos - ø75xø75</t>
+          <t>PVC - 750V (Prysmian) - 2.5 mm² - Azul claro</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D23" s="25" t="n">
-        <v>9</v>
+        <v>418.94</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>292.9</v>
+        <v>3.09</v>
       </c>
       <c r="F23" s="27" t="n">
-        <v>2636.1</v>
+        <v>1294.5246</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>1</v>
@@ -8788,7 +8464,7 @@
       </c>
       <c r="B24" s="24" t="inlineStr">
         <is>
-          <t>XLPE - 1kV (Prysmian) - 120 mm² - Azul claro</t>
+          <t>PEAD - Polietileno de Alta Densidade - Fita Sinalizadora de Conduto de Energia Elétrica</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -8797,13 +8473,13 @@
         </is>
       </c>
       <c r="D24" s="25" t="n">
-        <v>78.40000000000001</v>
+        <v>63.4</v>
       </c>
       <c r="E24" s="26" t="n">
-        <v>24.84</v>
+        <v>23.3</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>1947.456</v>
+        <v>1477.22</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>1</v>
@@ -8820,22 +8496,22 @@
       </c>
       <c r="B25" s="24" t="inlineStr">
         <is>
-          <t>XLPE - 1kV (Prysmian) - 120 mm² - Branco</t>
+          <t>Alarme - Central de Alarme de Incendio Endereçável</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D25" s="25" t="n">
-        <v>78.40000000000001</v>
+        <v>1</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>24.84</v>
+        <v>1348.75</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>1947.456</v>
+        <v>1348.75</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>1</v>
@@ -8852,7 +8528,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>XLPE - 1kV (Prysmian) - 120 mm² - Preto</t>
+          <t>Tubo - PPR - PN 20 - 25</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -8861,13 +8537,13 @@
         </is>
       </c>
       <c r="D26" s="25" t="n">
-        <v>78.40000000000001</v>
+        <v>99.86</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>24.84</v>
+        <v>11.66</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>1947.456</v>
+        <v>1164.3676</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>1</v>
@@ -8884,22 +8560,22 @@
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>XLPE - 1kV (Prysmian) - 120 mm² - Vermelho</t>
+          <t>Base Misturador Monocomando para Chuveiro 3/4, Bases - Docol - ø25xø25xø25</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D27" s="25" t="n">
-        <v>78.40000000000001</v>
+        <v>4</v>
       </c>
       <c r="E27" s="26" t="n">
-        <v>24.84</v>
+        <v>320</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>1947.456</v>
+        <v>1280</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>1</v>
@@ -8916,22 +8592,22 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>QUADRO DE DISTRIBUIÇÃO CARREGADOR VEICULAR - 1800X800X250 até 30</t>
+          <t>PVC - 750V (Prysmian) - 1.5 mm² - Amarelo</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D28" s="25" t="n">
-        <v>1</v>
+        <v>444</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>2500</v>
+        <v>2.09</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>2500</v>
+        <v>927.9599999999999</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>1</v>
@@ -8948,7 +8624,7 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>CAIXA DE PASSAGEM - PISO - Tampa 65x45 - R1</t>
+          <t>Conector Macho 63x2, PPR Termofusão - TIGRE - ø63xø63</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -8957,13 +8633,13 @@
         </is>
       </c>
       <c r="D29" s="25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>560.1799999999999</v>
+        <v>145.82</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>2240.72</v>
+        <v>1166.56</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>1</v>
@@ -8980,29 +8656,29 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra para instalações de sistema preventivo de incêndio *</t>
+          <t>Válvula de esfera com alavanca azul 1 1/2" - DocolBásicos - ø50xø50</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D30" s="25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30" s="26" t="n">
-        <v>2000</v>
+        <v>225</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>2000</v>
+        <v>1125</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -9012,22 +8688,22 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>Válvula redutora de pressão 42LP - 3/4" - ø20xø20</t>
+          <t>AÇO GALVANIZADO - 3"</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D31" s="25" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E31" s="26" t="n">
-        <v>1984.85</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>1984.85</v>
+        <v>1052.88</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>1</v>
@@ -9044,22 +8720,22 @@
       </c>
       <c r="B32" s="24" t="inlineStr">
         <is>
-          <t>Filtro de água pluvial: ACQUASAVE VF1 - ø150xø100xø150xø100</t>
+          <t>Tubo - PVC Esgoto - Série Normal - 100</t>
         </is>
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>pç</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>1</v>
+        <v>48.67</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>1980</v>
+        <v>18.33</v>
       </c>
       <c r="F32" s="27" t="n">
-        <v>1980</v>
+        <v>892.1211</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>1</v>
@@ -9076,29 +8752,29 @@
       </c>
       <c r="B33" s="24" t="inlineStr">
         <is>
-          <t>Aprovação e legalização elétrico*</t>
+          <t>Válvula de esfera com alavanca azul 2 1/2" - DocolBásicos - ø75xø75</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>vb</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D33" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>1700</v>
+        <v>503.5</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>1700</v>
+        <v>1007</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="24" t="inlineStr">
         <is>
-          <t>paludo-volo-home</t>
+          <t>xpcon-marena</t>
         </is>
       </c>
     </row>
@@ -9108,22 +8784,22 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>PVC - 750V (Prysmian) - 2.5 mm² - Azul claro</t>
+          <t>BERMAD - Válvula de Retenção VA 407R - 2" - ø50xø50</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>pç</t>
         </is>
       </c>
       <c r="D34" s="25" t="n">
-        <v>418.94</v>
+        <v>1</v>
       </c>
       <c r="E34" s="26" t="n">
-        <v>3.09</v>
+        <v>965.0599999999999</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>1294.5246</v>
+        <v>965.0599999999999</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>1</v>
@@ -9150,7 +8826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9225,22 +8901,22 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>Instalação Completa de Elevador de Pessoas Definitivo *</t>
+          <t>Fechamento removível de abertura no piso do elevador em madeira</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>un</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>1</v>
+        <v>16.9338</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>152799.2</v>
+        <v>3829.2018</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>152799.2</v>
+        <v>64842.93744084</v>
       </c>
       <c r="G5" s="23" t="n">
         <v>1</v>
@@ -9257,7 +8933,7 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>Fechamento removível de abertura no piso do elevador em madeira</t>
+          <t>Acabamento em granito em piso de elevador *</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -9266,13 +8942,13 @@
         </is>
       </c>
       <c r="D6" s="25" t="n">
-        <v>16.9338</v>
+        <v>21.44</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>3829.2018</v>
+        <v>454.8995</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>64842.93744084</v>
+        <v>9753.04528</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>1</v>
@@ -9289,7 +8965,7 @@
       </c>
       <c r="B7" s="24" t="inlineStr">
         <is>
-          <t>Acabamento em granito em piso de elevador *</t>
+          <t>Mão de obra empreitada para regularização e pintura do fosso do elevador *</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -9298,13 +8974,13 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>21.44</v>
+        <v>101.28</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>454.8995</v>
+        <v>20</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>9753.04528</v>
+        <v>2025.6</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>1</v>
@@ -9321,7 +8997,7 @@
       </c>
       <c r="B8" s="24" t="inlineStr">
         <is>
-          <t>Mão de obra empreitada para regularização e pintura do fosso do elevador *</t>
+          <t>Fechamento removível de vãos de porta de elevador em madeira *</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -9330,13 +9006,13 @@
         </is>
       </c>
       <c r="D8" s="25" t="n">
-        <v>101.28</v>
+        <v>12.18</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>20</v>
+        <v>60.8313</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>2025.6</v>
+        <v>740.9252339999999</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>1</v>
@@ -9353,7 +9029,7 @@
       </c>
       <c r="B9" s="24" t="inlineStr">
         <is>
-          <t>Fechamento removível de vãos de porta de elevador em madeira *</t>
+          <t>Pintura com tinta látex acrílica em fosso do elevador, 1 demão *</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -9362,82 +9038,18 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>12.18</v>
+        <v>101.28</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>60.8313</v>
+        <v>4.8</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>740.9252339999999</v>
+        <v>486.144</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Pintura com tinta látex acrílica em fosso do elevador, 1 demão *</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>101.28</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>486.144</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="24" t="inlineStr">
-        <is>
-          <t>paludo-volo-home</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>Alarme e Monitoramento de Obra *</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>vb</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>paludo-volo-home</t>
         </is>
